--- a/data/nomination/stellar/male/02-male-nomination.xlsx
+++ b/data/nomination/stellar/male/02-male-nomination.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -557,21 +557,13 @@
           <t>你的名字。</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>神木隆之介</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tachibana Taki</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -600,21 +592,13 @@
           <t>NO GAME NO LIFE 游戏人生</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>松冈祯丞</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Riku Dola</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -643,21 +627,13 @@
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>内山昂辉</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Otosaka Yū</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -686,21 +662,13 @@
           <t>进击的巨人</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>神谷浩史</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Levi</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -729,21 +697,13 @@
           <t>咒术回战</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>中村悠一</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Gojō Satoru</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -772,11 +732,7 @@
           <t>迷宫饭</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>熊谷健太郎</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -951,11 +907,7 @@
           <t>我独自升级</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>坂泰斗</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -990,21 +942,13 @@
           <t>路人超能100</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>樱井孝宏</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Reigen Arataka</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1068,11 +1012,7 @@
           <t>Unnamed Memory</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>中岛良树</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1142,21 +1082,13 @@
           <t>辉夜大小姐想让我告白～天才们的恋爱头脑战～</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>铃木崚汰</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Ishigami Yū</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1185,21 +1117,13 @@
           <t>可塑性记忆</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>内匠靖明</t>
-        </is>
-      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Mizugaki Tsukasa</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1228,11 +1152,7 @@
           <t>败犬女主太多了！</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>梅田修一朗</t>
-        </is>
-      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1267,21 +1187,13 @@
           <t>刀剑神域</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>松冈祯丞</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Kirigaya Kazuto</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1310,21 +1222,13 @@
           <t>JoJo的奇妙冒险</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>小野大辅</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Kūjō Jōtarō</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1353,21 +1257,13 @@
           <t>紫罗兰永恒花园</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>浪川大辅</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Gilbert Bougainvillea</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1396,21 +1292,13 @@
           <t>玉子市场</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>田丸笃志</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Ōji Mochizō</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1439,21 +1327,13 @@
           <t>死亡笔记</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>宫野真守</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Yagami Light</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1482,21 +1362,13 @@
           <t>魔法禁书目录</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>冈本信彦</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Accelerator</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1525,21 +1397,13 @@
           <t>葬送的芙莉莲</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>小林千晃</t>
-        </is>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Stark</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1568,21 +1432,13 @@
           <t>魔法禁书目录</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>阿部敦</t>
-        </is>
-      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Kamijō Tōma</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1611,21 +1467,13 @@
           <t>Re:从零开始的异世界生活</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>小林裕介</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Natsuki Subaru</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1654,21 +1502,13 @@
           <t>Fate系列</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>诹访部顺一</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Archer</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1697,21 +1537,13 @@
           <t>为美好的世界献上祝福！</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>福岛润</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Satō Kazuma</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1740,21 +1572,13 @@
           <t>堀与宫村</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>内山昂辉</t>
-        </is>
-      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Miyamura Izumi</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1783,21 +1607,13 @@
           <t>银魂</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>杉田智和</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Sakata Gintoki</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1826,11 +1642,7 @@
           <t>关于我在无意间被隔壁的天使变成废柴这件事</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>坂泰斗</t>
-        </is>
-      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1865,21 +1677,13 @@
           <t>间谍过家家</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>江口拓也</t>
-        </is>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Loid Forger</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1908,21 +1712,13 @@
           <t>火影忍者</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>井上和彦</t>
-        </is>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Hatake Kakashi</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1951,21 +1747,13 @@
           <t>进击的巨人</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>梶裕贵</t>
-        </is>
-      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Eren Yeager</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1994,21 +1782,13 @@
           <t>火影忍者</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>竹内顺子</t>
-        </is>
-      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Uzumaki Naruto</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2037,21 +1817,13 @@
           <t>龙与虎</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>间岛淳司</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Takasu Ryūji</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2080,21 +1852,13 @@
           <t>【我推的孩子】</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>大冢刚央</t>
-        </is>
-      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Hoshino Aquamarine</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2123,21 +1887,13 @@
           <t>Fate系列</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>神奈延年</t>
-        </is>
-      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Lancer</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2166,21 +1922,13 @@
           <t>海贼王</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>田中真弓</t>
-        </is>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Monkey D. Luffy</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2209,21 +1957,13 @@
           <t>文豪野犬</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>宫野真守</t>
-        </is>
-      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Dazai Osamu</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2637,21 +2377,13 @@
           <t>鲁邦三世</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>栗田贯一</t>
-        </is>
-      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Arsène Lupin III</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2680,21 +2412,13 @@
           <t>超超超超超喜欢你的100个女朋友</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>加藤涉</t>
-        </is>
-      </c>
+      <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Aijō Rentarō</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2828,21 +2552,13 @@
           <t>物语系列</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>神谷浩史</t>
-        </is>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Araragi Koyomi</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2871,11 +2587,7 @@
           <t>狼与香辛料</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>福山润</t>
-        </is>
-      </c>
+      <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2910,21 +2622,13 @@
           <t>HUNTER×HUNTER</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>伊濑茉莉也</t>
-        </is>
-      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Killua Zoldyck</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -3023,11 +2727,7 @@
           <t>地。-关于地球的运动-</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>坂本真绫</t>
-        </is>
-      </c>
+      <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3062,11 +2762,7 @@
           <t>胆大党</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>花江夏树</t>
-        </is>
-      </c>
+      <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3093,32 +2789,24 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>北原伊织</t>
+          <t>黑崎一护</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>碧蓝之海</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>内田雄马</t>
-        </is>
-      </c>
+          <t>BLEACH</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Kitahara Iori</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3136,32 +2824,24 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>辛耶·诺赞</t>
+          <t>中原中也</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>86 -不存在的战区-</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>千叶翔也</t>
-        </is>
-      </c>
+          <t>文豪野犬</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Shinei Nouzen</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3179,32 +2859,24 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>卫宫切嗣</t>
+          <t>夏亚·阿兹纳布尔</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Fate系列</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>小山力也</t>
-        </is>
-      </c>
+          <t>机动战士高达</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Emiya Kiritsugu</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3222,32 +2894,24 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>神田空太</t>
+          <t>绯村剑心</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>樱花庄的宠物女孩</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>松冈祯丞</t>
-        </is>
-      </c>
+          <t>浪客剑心</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Kanda Sorata</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3265,32 +2929,24 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>夜斗</t>
+          <t>樱木花道</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>野良神</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>神谷浩史</t>
-        </is>
-      </c>
+          <t>灌篮高手</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Yato</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3308,32 +2964,24 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>孙悟空</t>
+          <t>石神千空</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>龙珠</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>野泽雅子</t>
-        </is>
-      </c>
+          <t>Dr.STONE 石纪元</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Son Goku</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3351,32 +2999,24 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>宇智波带土</t>
+          <t>维吉尔</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>火影忍者</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>潘惠美</t>
-        </is>
-      </c>
+          <t>鬼泣系列</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Uchiha Obito</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3394,32 +3034,24 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>江户川柯南</t>
+          <t>壬氏</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>名侦探柯南</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>高山南</t>
-        </is>
-      </c>
+          <t>药屋少女的呢喃</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Edogawa Conan</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3437,32 +3069,24 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>木下秀吉</t>
+          <t>姚麟</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>笨蛋、测验、召唤兽</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>加藤英美里</t>
-        </is>
-      </c>
+          <t>钢之炼金术师</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Kinoshita Hideyoshi</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3480,32 +3104,24 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>李小狼</t>
+          <t>夏油杰</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>魔卡少女樱</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>熊井统子</t>
-        </is>
-      </c>
+          <t>咒术回战</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Li Syaoran</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3523,24 +3139,24 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>伏黑惠</t>
+          <t>的场静司</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>咒术回战</t>
+          <t>夏目友人帐</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3558,32 +3174,24 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>乔鲁诺·乔巴拿</t>
+          <t>特斯卡特利波卡</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>JoJo的奇妙冒险</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>小野贤章</t>
-        </is>
-      </c>
+          <t>Fate系列</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Giorno Giovanna</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3601,32 +3209,24 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>我妻善逸</t>
+          <t>名取周一</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>鬼灭之刃</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>下野纮</t>
-        </is>
-      </c>
+          <t>夏目友人帐</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Agatsuma Zenitsu</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -3644,32 +3244,24 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>齐木楠雄</t>
+          <t>米拉</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>齐木楠雄的灾难</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>神谷浩史</t>
-        </is>
-      </c>
+          <t>魔法少女与邪恶曾经敌对。</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Saiki Kusuo</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -3687,24 +3279,24 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>东方仗助</t>
+          <t>基洛斯·格拉纳多</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>JoJo的奇妙冒险</t>
+          <t>破烂千金被姐姐的原婚约者溺爱着</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -3722,29 +3314,21 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>和泉正宗</t>
+          <t>鲁迪乌斯·格雷拉特</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>埃罗芒阿老师</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>松冈祯丞</t>
-        </is>
-      </c>
+          <t>无职转生</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Izumi Masamune</t>
-        </is>
-      </c>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -3765,29 +3349,21 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>黑羽快斗</t>
+          <t>音无结弦</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>魔术快斗</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>山口胜平</t>
-        </is>
-      </c>
+          <t>Angel Beats!</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Kuroba Kaito</t>
-        </is>
-      </c>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -3808,18 +3384,18 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>杀老师</t>
+          <t>福部里志</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>暗杀教室</t>
+          <t>冰菓</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -3843,29 +3419,21 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>安昙小太郎</t>
+          <t>浅村悠太</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>月色真美</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>千叶翔也</t>
-        </is>
-      </c>
+          <t>义妹生活</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Azumi Kotarō</t>
-        </is>
-      </c>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -3886,29 +3454,21 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>渚薰</t>
+          <t>网代慎平</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>新世纪福音战士</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>石田彰</t>
-        </is>
-      </c>
+          <t>夏日重现</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Nagisa Kaworu</t>
-        </is>
-      </c>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -3929,29 +3489,21 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>樱满集</t>
+          <t>冈崎朋也</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>罪恶王冠</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>梶裕贵</t>
-        </is>
-      </c>
+          <t>CLANNAD</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Ōma Shū</t>
-        </is>
-      </c>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -3972,29 +3524,21 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>炼狱杏寿郎</t>
+          <t>五条新菜</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>鬼灭之刃</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>日野聪</t>
-        </is>
-      </c>
+          <t>更衣人偶坠入爱河</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Rengoku Kyōjurō</t>
-        </is>
-      </c>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -4015,29 +3559,21 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>安艺伦也</t>
+          <t>L Lawliet</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>路人女主的养成方法</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>松冈祯丞</t>
-        </is>
-      </c>
+          <t>死亡笔记</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Aki Tomoya</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -4058,29 +3594,21 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>内卷昴</t>
+          <t>五河士道</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>这个美术社大有问题！</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>小林裕介</t>
-        </is>
-      </c>
+          <t>约会大作战</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Uchimaki Subaru</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -4101,29 +3629,21 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>一条乐</t>
+          <t>宇智波佐助</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>伪恋</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>内山昂辉</t>
-        </is>
-      </c>
+          <t>火影忍者</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Ichijō Raku</t>
-        </is>
-      </c>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -4144,29 +3664,21 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>枣恭介</t>
+          <t>冈部伦太郎</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Little Busters!</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>绿川光</t>
-        </is>
-      </c>
+          <t>命运石之门</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Natsume Kyōsuke</t>
-        </is>
-      </c>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -4187,29 +3699,21 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>伊藤诚</t>
+          <t>春日野悠</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>School Days</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>平川大辅</t>
-        </is>
-      </c>
+          <t>缘之空</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Itō Makoto</t>
-        </is>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>False</t>
@@ -4230,18 +3734,18 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>国崎往人</t>
+          <t>由崎星空</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>AIR</t>
+          <t>总之就是非常可爱</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
@@ -4265,18 +3769,18 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>塔兹米</t>
+          <t>鲁路修·兰佩洛基</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>斩·赤红之瞳！</t>
+          <t>Code Geass</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
@@ -4300,18 +3804,18 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>海崎新太</t>
+          <t>迪奥·布兰度</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ReLIFE</t>
+          <t>JoJo的奇妙冒险</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -4335,18 +3839,18 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>平贺才人</t>
+          <t>西片</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>零之使魔</t>
+          <t>擅长捉弄的高木同学</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
@@ -4370,18 +3874,18 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>斑鸠夏生</t>
+          <t>绫小路清隆</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>ATRI -My Dear Moments-</t>
+          <t>欢迎来到实力至上主义的教室</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -4405,18 +3909,18 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>奥托·苏文</t>
+          <t>卫宫士郎</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Re:从零开始的异世界生活</t>
+          <t>Fate系列</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -4440,18 +3944,18 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>春原阳平</t>
+          <t>碇真嗣</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>CLANNAD</t>
+          <t>新世纪福音战士</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -4475,18 +3979,18 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>土间大平</t>
+          <t>宇智波鼬</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>干物妹！小埋</t>
+          <t>火影忍者</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
@@ -4510,18 +4014,18 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>高坂京介</t>
+          <t>森岛帆高</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>我的妹妹哪有这么可爱！</t>
+          <t>天气之子</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
@@ -4545,18 +4049,18 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>广</t>
+          <t>有马公生</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Darling in the FranXX</t>
+          <t>四月是你的谎言</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
@@ -4580,18 +4084,18 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>席德·卡盖诺</t>
+          <t>阿虚</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>想要成为影之实力者！</t>
+          <t>凉宫春日的忧郁</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
@@ -4615,18 +4119,18 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>久世政近</t>
+          <t>小智</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>不时轻声地以俄语遮羞的邻座艾莉同学</t>
+          <t>宝可梦</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
@@ -4650,18 +4154,18 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>苗木诚</t>
+          <t>宇佐美翔平</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>弹丸论破</t>
+          <t>薰香花朵凛然绽放</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
@@ -4685,18 +4189,18 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>日向翔阳</t>
+          <t>市川京太郎</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>排球少年！！</t>
+          <t>我心里危险的东西</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
@@ -4720,18 +4224,18 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>柚木普</t>
+          <t>乔瑟夫·乔斯达</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>地缚少年花子君</t>
+          <t>JoJo的奇妙冒险</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -4755,18 +4259,18 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>今村耕平</t>
+          <t>宇智波斑</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>碧蓝之海</t>
+          <t>火影忍者</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
@@ -4790,18 +4294,18 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>早川秋</t>
+          <t>波风水门</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>电锯人</t>
+          <t>火影忍者</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
@@ -4825,18 +4329,18 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>贝吉塔</t>
+          <t>吉尔伽美什</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>龙珠</t>
+          <t>Fate系列</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
@@ -4860,18 +4364,18 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>成步堂龙一</t>
+          <t>富冈义勇</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>逆转裁判系列</t>
+          <t>鬼灭之刃</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
@@ -4895,18 +4399,18 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>吉良吉影</t>
+          <t>乙骨忧太</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>JoJo的奇妙冒险</t>
+          <t>咒术回战</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
@@ -4930,18 +4434,18 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>影山茂夫</t>
+          <t>依田绚斗</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>路人超能100</t>
+          <t>薰香花朵凛然绽放</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
@@ -4965,18 +4469,18 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>冢本秀一</t>
+          <t>户冢彩加</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>吹响！上低音号</t>
+          <t>我的青春恋爱物语果然有问题。</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
@@ -5000,18 +4504,18 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>野原新之助</t>
+          <t>金木研</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>蜡笔小新</t>
+          <t>东京食尸鬼</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
@@ -5035,18 +4539,18 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>只野仁人</t>
+          <t>大卫·马丁内斯</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>古见同学有交流障碍症</t>
+          <t>赛博朋克 边缘行者</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
@@ -5070,18 +4574,18 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>夜守光</t>
+          <t>灶门炭治郎</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>彻夜之歌</t>
+          <t>鬼灭之刃</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
@@ -5105,18 +4609,18 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>老师</t>
+          <t>电次</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>蔚蓝档案</t>
+          <t>电锯人</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
@@ -5140,18 +4644,18 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>绫崎飒</t>
+          <t>北原伊织</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>旋风管家！</t>
+          <t>碧蓝之海</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
@@ -5175,18 +4679,18 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>夏尔·凡多姆海恩</t>
+          <t>辛耶·诺赞</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>黑执事</t>
+          <t>86 -不存在的战区-</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
@@ -5210,18 +4714,18 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>百夜米迦尔</t>
+          <t>卫宫切嗣</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>终结的炽天使</t>
+          <t>Fate系列</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
@@ -5245,18 +4749,18 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>九头龙八一</t>
+          <t>神田空太</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>龙王的工作！</t>
+          <t>樱花庄的宠物女孩</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
@@ -5280,18 +4784,18 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>可儿江西也</t>
+          <t>夜斗</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>甘城光辉游乐园</t>
+          <t>野良神</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
@@ -5315,18 +4819,18 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>狛枝凪斗</t>
+          <t>孙悟空</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>弹丸论破</t>
+          <t>龙珠</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
@@ -5350,18 +4854,18 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>爱德华·艾尔利克</t>
+          <t>宇智波带土</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>钢之炼金术师</t>
+          <t>火影忍者</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
@@ -5385,18 +4889,18 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>前原圭一</t>
+          <t>江户川柯南</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>寒蝉鸣泣之时</t>
+          <t>名侦探柯南</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
@@ -5420,18 +4924,18 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>犬夜叉</t>
+          <t>木下秀吉</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>犬夜叉</t>
+          <t>笨蛋、测验、召唤兽</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
@@ -5455,18 +4959,18 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>菲利克斯·阿盖尔</t>
+          <t>李小狼</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Re:从零开始的异世界生活</t>
+          <t>魔卡少女樱</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
@@ -5490,18 +4994,18 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>天王寺瑚太朗</t>
+          <t>伏黑惠</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Rewrite</t>
+          <t>咒术回战</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
@@ -5525,18 +5029,18 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>坂本</t>
+          <t>乔鲁诺·乔巴拿</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>在下坂本，有何贵干？</t>
+          <t>JoJo的奇妙冒险</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
@@ -5560,18 +5064,18 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>武藤游戏</t>
+          <t>我妻善逸</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>游戏王系列</t>
+          <t>鬼灭之刃</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
@@ -5595,18 +5099,18 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>江户川乱步</t>
+          <t>齐木楠雄</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>文豪野犬</t>
+          <t>齐木楠雄的灾难</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
@@ -5630,7 +5134,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>布鲁诺·布加拉提</t>
+          <t>东方仗助</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5641,7 +5145,7 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
@@ -5665,18 +5169,18 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>坂本太郎</t>
+          <t>和泉正宗</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>坂本日常</t>
+          <t>埃罗芒阿老师</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
@@ -5700,18 +5204,18 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>宿海仁太</t>
+          <t>黑羽快斗</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>我们仍未知道那天所看见的花的名字。</t>
+          <t>魔术快斗</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
@@ -5735,7 +5239,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>潮田渚</t>
+          <t>杀老师</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5746,7 +5250,7 @@
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
@@ -5770,18 +5274,18 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>木之本桃矢</t>
+          <t>安昙小太郎</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>魔卡少女樱</t>
+          <t>月色真美</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
@@ -5805,18 +5309,18 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>贝尔·克朗尼</t>
+          <t>渚薰</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>在地下城寻求邂逅是否搞错了什么</t>
+          <t>新世纪福音战士</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
@@ -5840,18 +5344,18 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>野崎梅太郎</t>
+          <t>樱满集</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>月刊少女野崎君</t>
+          <t>罪恶王冠</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
@@ -5875,18 +5379,18 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>埼玉</t>
+          <t>炼狱杏寿郎</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>一拳超人</t>
+          <t>鬼灭之刃</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
@@ -5910,18 +5414,18 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>雨宫莲</t>
+          <t>安艺伦也</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>女神异闻录5</t>
+          <t>路人女主的养成方法</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
@@ -5945,18 +5449,18 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>上杉风太郎</t>
+          <t>内卷昴</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>五等分的新娘</t>
+          <t>这个美术社大有问题！</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
@@ -5980,18 +5484,18 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>野比大雄</t>
+          <t>一条乐</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>哆啦A梦</t>
+          <t>伪恋</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
@@ -6015,18 +5519,18 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>时透无一郎</t>
+          <t>枣恭介</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>鬼灭之刃</t>
+          <t>Little Busters!</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
@@ -6050,18 +5554,18 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>岸边露伴</t>
+          <t>伊藤诚</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>JoJo的奇妙冒险</t>
+          <t>School Days</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -6071,6 +5575,1861 @@
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>国崎往人</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>塔兹米</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>斩·赤红之瞳！</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>海崎新太</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>ReLIFE</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>平贺才人</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>零之使魔</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>斑鸠夏生</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>ATRI -My Dear Moments-</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>奥托·苏文</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Re:从零开始的异世界生活</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>春原阳平</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>CLANNAD</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>土间大平</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>干物妹！小埋</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>高坂京介</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>我的妹妹哪有这么可爱！</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>广</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Darling in the FranXX</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>席德·卡盖诺</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>想要成为影之实力者！</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>久世政近</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>不时轻声地以俄语遮羞的邻座艾莉同学</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>苗木诚</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>弹丸论破</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>日向翔阳</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>排球少年！！</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>柚木普</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>地缚少年花子君</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>今村耕平</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>碧蓝之海</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>早川秋</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>电锯人</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>贝吉塔</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>龙珠</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>成步堂龙一</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>逆转裁判系列</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>吉良吉影</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>JoJo的奇妙冒险</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>影山茂夫</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>路人超能100</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>冢本秀一</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>吹响！上低音号</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>野原新之助</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>蜡笔小新</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>只野仁人</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>古见同学有交流障碍症</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>夜守光</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>彻夜之歌</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>老师</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>蔚蓝档案</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>绫崎飒</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>旋风管家！</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>夏尔·凡多姆海恩</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>黑执事</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>百夜米迦尔</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>终结的炽天使</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>九头龙八一</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>龙王的工作！</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>可儿江西也</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>甘城光辉游乐园</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>狛枝凪斗</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>弹丸论破</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>爱德华·艾尔利克</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>钢之炼金术师</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>前原圭一</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>寒蝉鸣泣之时</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>犬夜叉</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>犬夜叉</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>菲利克斯·阿盖尔</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Re:从零开始的异世界生活</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>天王寺瑚太朗</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>坂本</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>在下坂本，有何贵干？</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>武藤游戏</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>游戏王系列</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>江户川乱步</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>文豪野犬</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>布鲁诺·布加拉提</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>JoJo的奇妙冒险</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>坂本太郎</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>坂本日常</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>宿海仁太</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>我们仍未知道那天所看见的花的名字。</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>潮田渚</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>暗杀教室</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>木之本桃矢</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>魔卡少女樱</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>贝尔·克朗尼</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>在地下城寻求邂逅是否搞错了什么</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>野崎梅太郎</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>月刊少女野崎君</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>一拳超人</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>雨宫莲</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>女神异闻录5</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>上杉风太郎</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>五等分的新娘</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>野比大雄</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>哆啦A梦</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>时透无一郎</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>鬼灭之刃</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>07.12-07.19</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>恒星组提名-男性组别</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>岸边露伴</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>JoJo的奇妙冒险</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
